--- a/files/CHR/talk_黄蘭.xlsx
+++ b/files/CHR/talk_黄蘭.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\CHR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE27435A-6049-4C9E-B0FE-6AD589580C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258E0D4E-E749-4C3C-AB8A-357955885417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="27990" windowHeight="14415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8610" yWindow="885" windowWidth="27990" windowHeight="14415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="183">
   <si>
     <t>各キャラクタのランダムセリフ集。指定座標のセリフがあればそちらを優先してしゃべる。</t>
   </si>
@@ -564,6 +564,95 @@
     </rPh>
     <rPh sb="16" eb="17">
       <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12月21日主</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12月21日反応</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワイルドハント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワイルドハント反応</t>
+    <rPh sb="7" eb="9">
+      <t>ハンノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表で化け物が行列してるぜ、祭でもやるのかい</t>
+    <rPh sb="0" eb="1">
+      <t>オモテ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ギョウレツ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>マツリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>化け物にもフェスとかあんのかね、へっ</t>
+    <rPh sb="0" eb="1">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なんて化け物の量だ、ここももう限界だ…</t>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゲンカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乗るしかねえなこのウェーブに！</t>
+    <rPh sb="0" eb="1">
+      <t>ノ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -627,7 +716,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -647,6 +736,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -961,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:B134"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.75" style="6" customWidth="1"/>
@@ -1728,51 +1820,51 @@
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
-        <v>136</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>137</v>
+      <c r="A97" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B97" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
-        <v>138</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>139</v>
+      <c r="A98" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B98" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A99" t="s">
-        <v>140</v>
+      <c r="A99" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="B99" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A100" t="s">
-        <v>140</v>
+      <c r="A100" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="B100" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>140</v>
-      </c>
-      <c r="B101" t="s">
-        <v>143</v>
+        <v>136</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>140</v>
-      </c>
-      <c r="B102" t="s">
-        <v>144</v>
+        <v>138</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.4">
@@ -1780,7 +1872,7 @@
         <v>140</v>
       </c>
       <c r="B103" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.4">
@@ -1788,174 +1880,206 @@
         <v>140</v>
       </c>
       <c r="B104" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>140</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>147</v>
+      <c r="B105" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B106" s="1"/>
+      <c r="A106" t="s">
+        <v>140</v>
+      </c>
+      <c r="B106" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>148</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
+      </c>
+      <c r="B107" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>148</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
+      </c>
+      <c r="B108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>140</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A110" t="s">
-        <v>151</v>
-      </c>
-      <c r="B110" t="s">
-        <v>152</v>
-      </c>
+      <c r="B110" s="1"/>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>151</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
+        <v>148</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
         <v>151</v>
       </c>
-      <c r="B112" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A113" t="s">
-        <v>151</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>155</v>
+      <c r="B114" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>156</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="B116" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
+        <v>151</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
         <v>156</v>
       </c>
-      <c r="B117" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A118" t="s">
-        <v>156</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>160</v>
+      <c r="B119" s="4" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>161</v>
-      </c>
-      <c r="B121" t="s">
-        <v>163</v>
+        <v>156</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
+        <v>156</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
         <v>161</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A123" t="s">
-        <v>161</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>165</v>
+      <c r="B124" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>166</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
+      </c>
+      <c r="B125" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>166</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>166</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A128" t="s">
-        <v>166</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>170</v>
+        <v>161</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
         <v>166</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="B129" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>166</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A131" t="s">
+        <v>166</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A132" t="s">
+        <v>166</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>166</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B130" s="2"/>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B134" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
